--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R72d46651656e497b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf21cc2e6abf14800"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf21cc2e6abf14800"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4d1ffcb743f44596"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4d1ffcb743f44596"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R50325cc2bc1f47e7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R50325cc2bc1f47e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Red6ed89c3fb14960"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Red6ed89c3fb14960"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R001232d139984267"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R001232d139984267"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R03bbd18afa084281"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R03bbd18afa084281"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8e0eb4c3c3664f8f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8e0eb4c3c3664f8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R35c87b3fa91945aa"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R35c87b3fa91945aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb6d76e59a8454437"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb6d76e59a8454437"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R91c4a573e2584e62"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R91c4a573e2584e62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9092f50d822c4fb4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_DuplicateValues/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9092f50d822c4fb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf23f65d416cd46ca"/>
   </x:sheets>
 </x:workbook>
 </file>
